--- a/datos_rendimiento_pc.xlsx
+++ b/datos_rendimiento_pc.xlsx
@@ -451,13 +451,13 @@
         <v>150</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05261874198913574</v>
+        <v>0.002789735794067383</v>
       </c>
       <c r="D2" t="n">
-        <v>65.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="E2" t="n">
-        <v>70.59999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         <v>300</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008281946182250977</v>
+        <v>0.01998066902160645</v>
       </c>
       <c r="D3" t="n">
-        <v>23.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>70.59999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         <v>450</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02295398712158203</v>
+        <v>0.02567315101623535</v>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>48.1</v>
       </c>
       <c r="E4" t="n">
-        <v>70.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -502,13 +502,13 @@
         <v>600</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06403684616088867</v>
+        <v>0.0644690990447998</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>70.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -519,13 +519,13 @@
         <v>750</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09672307968139648</v>
+        <v>0.129737377166748</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="E6" t="n">
-        <v>70.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -536,13 +536,13 @@
         <v>900</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1649839878082275</v>
+        <v>0.1786243915557861</v>
       </c>
       <c r="D7" t="n">
-        <v>6.9</v>
+        <v>24.1</v>
       </c>
       <c r="E7" t="n">
-        <v>70.8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>1050</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2238078117370605</v>
+        <v>0.2565979957580566</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="E8" t="n">
-        <v>70.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -570,13 +570,13 @@
         <v>1200</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3183679580688477</v>
+        <v>0.7118704319000244</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="E9" t="n">
-        <v>70.7</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="10">
@@ -587,13 +587,13 @@
         <v>1350</v>
       </c>
       <c r="C10" t="n">
-        <v>0.471954345703125</v>
+        <v>0.5219666957855225</v>
       </c>
       <c r="D10" t="n">
-        <v>10.7</v>
+        <v>4.2</v>
       </c>
       <c r="E10" t="n">
-        <v>70.90000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="11">
@@ -604,13 +604,13 @@
         <v>1500</v>
       </c>
       <c r="C11" t="n">
-        <v>0.637073278427124</v>
+        <v>0.6474697589874268</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="12">
@@ -621,13 +621,13 @@
         <v>1650</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9485538005828857</v>
+        <v>0.8924121856689453</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>71.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -638,13 +638,13 @@
         <v>1800</v>
       </c>
       <c r="C13" t="n">
-        <v>1.183269500732422</v>
+        <v>1.13275408744812</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="E13" t="n">
-        <v>71.3</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="14">
@@ -655,13 +655,13 @@
         <v>1950</v>
       </c>
       <c r="C14" t="n">
-        <v>1.380201101303101</v>
+        <v>1.40861701965332</v>
       </c>
       <c r="D14" t="n">
-        <v>22.7</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>71.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -672,13 +672,13 @@
         <v>2100</v>
       </c>
       <c r="C15" t="n">
-        <v>2.700486183166504</v>
+        <v>1.704900026321411</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="E15" t="n">
-        <v>72.3</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -689,13 +689,13 @@
         <v>2250</v>
       </c>
       <c r="C16" t="n">
-        <v>2.272220373153687</v>
+        <v>2.091877937316895</v>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="E16" t="n">
-        <v>72.59999999999999</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="17">
@@ -706,13 +706,13 @@
         <v>2400</v>
       </c>
       <c r="C17" t="n">
-        <v>2.46446418762207</v>
+        <v>2.487946033477783</v>
       </c>
       <c r="D17" t="n">
-        <v>53.6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>72.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -723,13 +723,13 @@
         <v>2550</v>
       </c>
       <c r="C18" t="n">
-        <v>3.365754365921021</v>
+        <v>3.035715341567993</v>
       </c>
       <c r="D18" t="n">
-        <v>53.6</v>
+        <v>21.4</v>
       </c>
       <c r="E18" t="n">
-        <v>72.8</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -740,13 +740,13 @@
         <v>2700</v>
       </c>
       <c r="C19" t="n">
-        <v>3.432026863098145</v>
+        <v>3.516082048416138</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>73.09999999999999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -757,13 +757,13 @@
         <v>2850</v>
       </c>
       <c r="C20" t="n">
-        <v>3.774803876876831</v>
+        <v>4.141282320022583</v>
       </c>
       <c r="D20" t="n">
-        <v>68.8</v>
+        <v>42.9</v>
       </c>
       <c r="E20" t="n">
-        <v>73.09999999999999</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="21">
@@ -774,13 +774,13 @@
         <v>3000</v>
       </c>
       <c r="C21" t="n">
-        <v>4.568444967269897</v>
+        <v>4.740007877349854</v>
       </c>
       <c r="D21" t="n">
-        <v>27.6</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="n">
-        <v>73.09999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="22">
@@ -791,13 +791,13 @@
         <v>3150</v>
       </c>
       <c r="C22" t="n">
-        <v>5.217283487319946</v>
+        <v>6.015487670898438</v>
       </c>
       <c r="D22" t="n">
-        <v>8.300000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="E22" t="n">
-        <v>73.3</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -808,13 +808,13 @@
         <v>3300</v>
       </c>
       <c r="C23" t="n">
-        <v>5.762357711791992</v>
+        <v>6.760826110839844</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="E23" t="n">
-        <v>73.3</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -825,13 +825,13 @@
         <v>3450</v>
       </c>
       <c r="C24" t="n">
-        <v>6.566212892532349</v>
+        <v>7.564680337905884</v>
       </c>
       <c r="D24" t="n">
-        <v>46.4</v>
+        <v>57.1</v>
       </c>
       <c r="E24" t="n">
-        <v>73.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -842,13 +842,13 @@
         <v>3600</v>
       </c>
       <c r="C25" t="n">
-        <v>7.569157600402832</v>
+        <v>8.416673898696899</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="E25" t="n">
-        <v>74</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -859,13 +859,13 @@
         <v>3750</v>
       </c>
       <c r="C26" t="n">
-        <v>8.819575548171997</v>
+        <v>9.284353017807007</v>
       </c>
       <c r="D26" t="n">
-        <v>64.3</v>
+        <v>3.6</v>
       </c>
       <c r="E26" t="n">
-        <v>74.5</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="27">
@@ -876,13 +876,13 @@
         <v>3900</v>
       </c>
       <c r="C27" t="n">
-        <v>9.385311841964722</v>
+        <v>11.12141108512878</v>
       </c>
       <c r="D27" t="n">
-        <v>15.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>74.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         <v>4050</v>
       </c>
       <c r="C28" t="n">
-        <v>10.47558331489563</v>
+        <v>13.25630593299866</v>
       </c>
       <c r="D28" t="n">
-        <v>3.8</v>
+        <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>74.7</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -910,13 +910,13 @@
         <v>4200</v>
       </c>
       <c r="C29" t="n">
-        <v>11.78580451011658</v>
+        <v>16.06571292877197</v>
       </c>
       <c r="D29" t="n">
-        <v>18.5</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>74.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         <v>4350</v>
       </c>
       <c r="C30" t="n">
-        <v>12.8296115398407</v>
+        <v>17.52909803390503</v>
       </c>
       <c r="D30" t="n">
-        <v>3.6</v>
+        <v>100</v>
       </c>
       <c r="E30" t="n">
-        <v>75.2</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -944,13 +944,13 @@
         <v>4500</v>
       </c>
       <c r="C31" t="n">
-        <v>14.17196178436279</v>
+        <v>18.90233993530273</v>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="E31" t="n">
-        <v>75.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +961,13 @@
         <v>4650</v>
       </c>
       <c r="C32" t="n">
-        <v>15.79969930648804</v>
+        <v>20.64908194541931</v>
       </c>
       <c r="D32" t="n">
-        <v>67.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E32" t="n">
-        <v>75.40000000000001</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="33">
@@ -978,13 +978,13 @@
         <v>4800</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2709801197052</v>
+        <v>24.56105780601501</v>
       </c>
       <c r="D33" t="n">
-        <v>17.4</v>
+        <v>21.4</v>
       </c>
       <c r="E33" t="n">
-        <v>75.5</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -995,13 +995,13 @@
         <v>4950</v>
       </c>
       <c r="C34" t="n">
-        <v>18.66600131988525</v>
+        <v>53.00228309631348</v>
       </c>
       <c r="D34" t="n">
-        <v>14.8</v>
+        <v>23.1</v>
       </c>
       <c r="E34" t="n">
-        <v>75.59999999999999</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         <v>5100</v>
       </c>
       <c r="C35" t="n">
-        <v>20.52901792526245</v>
+        <v>48.14913487434387</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>76</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="36">
@@ -1029,13 +1029,13 @@
         <v>5250</v>
       </c>
       <c r="C36" t="n">
-        <v>22.22359037399292</v>
+        <v>51.70857548713684</v>
       </c>
       <c r="D36" t="n">
-        <v>35.7</v>
+        <v>18.5</v>
       </c>
       <c r="E36" t="n">
-        <v>76.3</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1046,13 +1046,13 @@
         <v>5400</v>
       </c>
       <c r="C37" t="n">
-        <v>23.92162752151489</v>
+        <v>79.04299545288086</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37" t="n">
-        <v>76.7</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="38">
@@ -1063,13 +1063,13 @@
         <v>5550</v>
       </c>
       <c r="C38" t="n">
-        <v>26.50588822364807</v>
+        <v>50.78942346572876</v>
       </c>
       <c r="D38" t="n">
-        <v>92.90000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="E38" t="n">
-        <v>76.90000000000001</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="39">
@@ -1080,13 +1080,13 @@
         <v>5700</v>
       </c>
       <c r="C39" t="n">
-        <v>46.53732371330261</v>
+        <v>66.28885078430176</v>
       </c>
       <c r="D39" t="n">
-        <v>63</v>
+        <v>21.4</v>
       </c>
       <c r="E39" t="n">
-        <v>77.2</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1097,13 +1097,13 @@
         <v>5850</v>
       </c>
       <c r="C40" t="n">
-        <v>49.10166549682617</v>
+        <v>74.71812510490417</v>
       </c>
       <c r="D40" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>77.3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
@@ -1114,13 +1114,13 @@
         <v>6000</v>
       </c>
       <c r="C41" t="n">
-        <v>44.03692054748535</v>
+        <v>99.17939186096191</v>
       </c>
       <c r="D41" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="E41" t="n">
-        <v>77.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
   </sheetData>
